--- a/JK-RFT Electrical/Documents/Connection diagram.xlsx
+++ b/JK-RFT Electrical/Documents/Connection diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sutdapac-my.sharepoint.com/personal/zhaoen_koh_mymail_sutd_edu_sg/Documents/02.1_Git Projects/PSL-JK-RTF/Retro Phone Rotary Numpad/JK-RFT Electrical/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="481" documentId="8_{49C9851E-31B7-42EE-991F-29E818C34283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85D273D9-C001-4AEB-BE8C-EF758D64FF04}"/>
+  <xr:revisionPtr revIDLastSave="488" documentId="8_{49C9851E-31B7-42EE-991F-29E818C34283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E17FA4F-F558-4B7C-B53A-8F98F668C0D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A807213-2A43-447B-BD4F-9D82DAB9230C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="104">
   <si>
     <t>SWCLK</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>Raspberry Pi Pico</t>
+  </si>
+  <si>
+    <t>..</t>
   </si>
 </sst>
 </file>
@@ -757,12 +760,90 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -779,84 +860,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -885,6 +888,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1204,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E339727-D21D-4100-B781-ADD16096FB71}">
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="1"/>
@@ -1215,802 +1222,810 @@
     <col min="13" max="13" width="3" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16" width="8.88671875" style="1"/>
     <col min="17" max="17" width="3" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.88671875" style="1"/>
+    <col min="18" max="18" width="8.88671875" style="1"/>
+    <col min="19" max="19" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="19" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="18" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="D7" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="30"/>
+      <c r="F7" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="20">
+        <v>1</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="22">
+        <v>40</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="D8" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="30"/>
+      <c r="F8" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="27"/>
+      <c r="I8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="21">
+        <v>2</v>
+      </c>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="23">
+        <v>39</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="L9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" s="21">
+        <v>3</v>
+      </c>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="23">
+        <v>38</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="D10" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="28" t="s">
+      <c r="C10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="34"/>
+      <c r="F10" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="M10" s="21">
+        <v>4</v>
+      </c>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="23">
+        <v>37</v>
+      </c>
+      <c r="R10" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="C11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="35"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="M11" s="21">
+        <v>5</v>
+      </c>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="23">
+        <v>36</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="D12" s="35"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="21">
+        <v>6</v>
+      </c>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="23">
+        <v>35</v>
+      </c>
+      <c r="R12" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="D13" s="37"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="21">
+        <v>7</v>
+      </c>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="23">
+        <v>34</v>
+      </c>
+      <c r="R13" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="W13" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="X13" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y13" s="27"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="L14" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="21">
+        <v>8</v>
+      </c>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="23">
+        <v>33</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="D15" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="30"/>
+      <c r="F15" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="21">
+        <v>9</v>
+      </c>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="23">
+        <v>32</v>
+      </c>
+      <c r="R15" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W15" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="X15" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y15" s="27"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="D16" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="30"/>
+      <c r="F16" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="M16" s="21">
+        <v>10</v>
+      </c>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="23">
+        <v>31</v>
+      </c>
+      <c r="R16" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W16" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="X16" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y16" s="27"/>
+    </row>
+    <row r="17" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D17" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="30"/>
+      <c r="F17" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="21">
+        <v>11</v>
+      </c>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="23">
+        <v>30</v>
+      </c>
+      <c r="R17" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D18" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="30"/>
+      <c r="F18" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="M18" s="21">
+        <v>12</v>
+      </c>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="23">
+        <v>29</v>
+      </c>
+      <c r="R18" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="W18" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="X18" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y18" s="27"/>
+    </row>
+    <row r="19" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="L19" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M19" s="21">
+        <v>13</v>
+      </c>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="23">
+        <v>28</v>
+      </c>
+      <c r="R19" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D20" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="30"/>
+      <c r="F20" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="M20" s="21">
+        <v>14</v>
+      </c>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="23">
+        <v>27</v>
+      </c>
+      <c r="R20" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W20" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="X20" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y20" s="27"/>
+    </row>
+    <row r="21" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D21" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="30"/>
+      <c r="F21" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="M21" s="21">
+        <v>15</v>
+      </c>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="23">
+        <v>26</v>
+      </c>
+      <c r="R21" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W21" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="Y21" s="27"/>
+      <c r="Z21" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D22" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="30"/>
+      <c r="F22" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="21">
+        <v>16</v>
+      </c>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="23">
+        <v>25</v>
+      </c>
+      <c r="R22" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W22" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="Y22" s="27"/>
+      <c r="Z22" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="D23" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="30"/>
+      <c r="F23" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" s="21">
+        <v>17</v>
+      </c>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="23">
+        <v>24</v>
+      </c>
+      <c r="R23" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W23" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="X23" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y23" s="27"/>
+    </row>
+    <row r="24" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="L24" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M24" s="21">
+        <v>18</v>
+      </c>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="23">
+        <v>23</v>
+      </c>
+      <c r="R24" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D25" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="30"/>
+      <c r="F25" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" s="21">
+        <v>19</v>
+      </c>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="23">
+        <v>22</v>
+      </c>
+      <c r="R25" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="W25" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="X25" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y25" s="27"/>
+    </row>
+    <row r="26" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D26" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="30"/>
+      <c r="F26" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" s="25">
+        <v>20</v>
+      </c>
+      <c r="N26" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="28"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="26">
+        <v>21</v>
+      </c>
+      <c r="R26" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W26" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L10" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="M10" s="31">
+      <c r="X26" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y26" s="27"/>
+    </row>
+    <row r="27" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N27" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="O27" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="N10" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="33">
-        <v>40</v>
-      </c>
-      <c r="R10" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="D11" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="M11" s="32">
+      <c r="P27" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="34">
-        <v>39</v>
-      </c>
-      <c r="R11" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="L12" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="M12" s="32">
-        <v>3</v>
-      </c>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="34">
-        <v>38</v>
-      </c>
-      <c r="R12" s="17" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="C13" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K13" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="M13" s="32">
-        <v>4</v>
-      </c>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="34">
-        <v>37</v>
-      </c>
-      <c r="R13" s="29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="C14" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="M14" s="32">
-        <v>5</v>
-      </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="34">
-        <v>36</v>
-      </c>
-      <c r="R14" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="D15" s="9"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="32">
-        <v>6</v>
-      </c>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="34">
-        <v>35</v>
-      </c>
-      <c r="R15" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="D16" s="11"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K16" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="M16" s="32">
-        <v>7</v>
-      </c>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="34">
-        <v>34</v>
-      </c>
-      <c r="R16" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="W16" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="X16" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y16" s="5"/>
-    </row>
-    <row r="17" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="L17" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="M17" s="32">
-        <v>8</v>
-      </c>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="34">
-        <v>33</v>
-      </c>
-      <c r="R17" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L18" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="M18" s="32">
-        <v>9</v>
-      </c>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="34">
-        <v>32</v>
-      </c>
-      <c r="R18" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="W18" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="X18" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y18" s="5"/>
-    </row>
-    <row r="19" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D19" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L19" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="M19" s="32">
-        <v>10</v>
-      </c>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="34">
-        <v>31</v>
-      </c>
-      <c r="R19" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="W19" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="X19" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y19" s="5"/>
-    </row>
-    <row r="20" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D20" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L20" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="M20" s="32">
-        <v>11</v>
-      </c>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="34">
-        <v>30</v>
-      </c>
-      <c r="R20" s="29" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D21" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L21" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="M21" s="32">
-        <v>12</v>
-      </c>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="34">
-        <v>29</v>
-      </c>
-      <c r="R21" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="W21" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="X21" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y21" s="5"/>
-    </row>
-    <row r="22" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="L22" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="M22" s="32">
-        <v>13</v>
-      </c>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="34">
-        <v>28</v>
-      </c>
-      <c r="R22" s="17" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D23" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L23" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="M23" s="32">
-        <v>14</v>
-      </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="34">
-        <v>27</v>
-      </c>
-      <c r="R23" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="W23" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="X23" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y23" s="5"/>
-    </row>
-    <row r="24" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D24" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L24" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="M24" s="32">
-        <v>15</v>
-      </c>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="34">
-        <v>26</v>
-      </c>
-      <c r="R24" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="S24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W24" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5"/>
-      <c r="Z24" s="16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D25" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L25" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" s="32">
-        <v>16</v>
-      </c>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="34">
-        <v>25</v>
-      </c>
-      <c r="R25" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="W25" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
-      <c r="Z25" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D26" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L26" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="M26" s="32">
-        <v>17</v>
-      </c>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="34">
-        <v>24</v>
-      </c>
-      <c r="R26" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="W26" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="X26" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y26" s="5"/>
-    </row>
-    <row r="27" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="L27" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="M27" s="32">
-        <v>18</v>
-      </c>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="34">
-        <v>23</v>
-      </c>
-      <c r="R27" s="17" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D28" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L28" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="M28" s="32">
-        <v>19</v>
-      </c>
-      <c r="N28" s="38"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="34">
-        <v>22</v>
-      </c>
-      <c r="R28" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="U28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="W28" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="X28" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y28" s="5"/>
-    </row>
-    <row r="29" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D29" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L29" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="M29" s="36">
-        <v>20</v>
-      </c>
-      <c r="N29" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="O29" s="20"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="37">
-        <v>21</v>
-      </c>
-      <c r="R29" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="S29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="U29" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="W29" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="X29" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y29" s="5"/>
-    </row>
-    <row r="30" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N30" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="O30" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="P30" s="23" t="s">
-        <v>2</v>
+    </row>
+    <row r="32" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="I32" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="X23:Y25"/>
-    <mergeCell ref="N10:P28"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="X26:Y26"/>
+    <mergeCell ref="X25:Y25"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="X20:Y22"/>
+    <mergeCell ref="N7:P25"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
     <mergeCell ref="X18:Y18"/>
     <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="X26:Y26"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="D13:E16"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="D10:E13"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JK-RFT Electrical/Documents/Connection diagram.xlsx
+++ b/JK-RFT Electrical/Documents/Connection diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sutdapac-my.sharepoint.com/personal/zhaoen_koh_mymail_sutd_edu_sg/Documents/02.1_Git Projects/PSL-JK-RTF/Retro Phone Rotary Numpad/JK-RFT Electrical/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="488" documentId="8_{49C9851E-31B7-42EE-991F-29E818C34283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E17FA4F-F558-4B7C-B53A-8F98F668C0D7}"/>
+  <xr:revisionPtr revIDLastSave="537" documentId="8_{49C9851E-31B7-42EE-991F-29E818C34283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{214891BE-A38F-456B-9F39-B418BBB27579}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A807213-2A43-447B-BD4F-9D82DAB9230C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="117">
   <si>
     <t>SWCLK</t>
   </si>
@@ -263,12 +263,6 @@
     <t>ENC 10</t>
   </si>
   <si>
-    <t>OUT A</t>
-  </si>
-  <si>
-    <t>Switch</t>
-  </si>
-  <si>
     <t>ENC 1-10</t>
   </si>
   <si>
@@ -290,18 +284,6 @@
     <t>KEYS</t>
   </si>
   <si>
-    <t>+</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>÷</t>
-  </si>
-  <si>
-    <t>×</t>
-  </si>
-  <si>
     <t>AUDIO AMP 1&amp;2</t>
   </si>
   <si>
@@ -317,9 +299,6 @@
     <t>SD</t>
   </si>
   <si>
-    <t>Mode</t>
-  </si>
-  <si>
     <t>LEGEND</t>
   </si>
   <si>
@@ -351,6 +330,66 @@
   </si>
   <si>
     <t>..</t>
+  </si>
+  <si>
+    <t>GND (1)</t>
+  </si>
+  <si>
+    <t>OUT A (2)</t>
+  </si>
+  <si>
+    <t>GND (3)</t>
+  </si>
+  <si>
+    <t>Switch (4)</t>
+  </si>
+  <si>
+    <t>÷ (2)</t>
+  </si>
+  <si>
+    <t>× (2)</t>
+  </si>
+  <si>
+    <t>+ (2)</t>
+  </si>
+  <si>
+    <t>-  (2)</t>
+  </si>
+  <si>
+    <t>Switch (2)</t>
+  </si>
+  <si>
+    <t>Mode (2)</t>
+  </si>
+  <si>
+    <t>N1</t>
+  </si>
+  <si>
+    <t>N2</t>
+  </si>
+  <si>
+    <t>N3</t>
+  </si>
+  <si>
+    <t>N4</t>
+  </si>
+  <si>
+    <t>N5</t>
+  </si>
+  <si>
+    <t>N6</t>
+  </si>
+  <si>
+    <t>N7</t>
+  </si>
+  <si>
+    <t>N8</t>
+  </si>
+  <si>
+    <t>N9</t>
+  </si>
+  <si>
+    <t>N0</t>
   </si>
 </sst>
 </file>
@@ -746,7 +785,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -862,6 +901,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1227,54 +1276,57 @@
     <col min="20" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
       <c r="D1" s="27"/>
       <c r="E1" s="27"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C7" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D7" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="17" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>57</v>
@@ -1295,7 +1347,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="28" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="O7" s="28"/>
       <c r="P7" s="28"/>
@@ -1306,13 +1358,16 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C8" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D8" s="30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E8" s="30"/>
       <c r="F8" s="17" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="H8" s="27"/>
       <c r="I8" s="2" t="s">
@@ -1340,7 +1395,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="L9" s="7" t="s">
         <v>1</v>
       </c>
@@ -1357,7 +1412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C10" s="8" t="s">
         <v>63</v>
       </c>
@@ -1390,7 +1445,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C11" s="5" t="s">
         <v>1</v>
       </c>
@@ -1421,7 +1476,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="D12" s="35"/>
       <c r="E12" s="36"/>
       <c r="F12" s="15" t="s">
@@ -1455,7 +1510,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="D13" s="37"/>
       <c r="E13" s="38"/>
       <c r="F13" s="15" t="s">
@@ -1489,14 +1544,17 @@
         <v>50</v>
       </c>
       <c r="W13" s="17" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="X13" s="27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Y13" s="27"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z13" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="L14" s="7" t="s">
         <v>1</v>
       </c>
@@ -1516,13 +1574,19 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C15" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D15" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="30"/>
+      <c r="E15" s="40"/>
       <c r="F15" s="17" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>107</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>52</v>
@@ -1552,20 +1616,29 @@
         <v>51</v>
       </c>
       <c r="W15" s="17" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="X15" s="27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Y15" s="27"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z15" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C16" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D16" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="30"/>
+      <c r="E16" s="40"/>
       <c r="F16" s="17" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>108</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>51</v>
@@ -1594,21 +1667,30 @@
       <c r="T16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W16" s="17" t="s">
-        <v>84</v>
+      <c r="W16" s="39" t="s">
+        <v>104</v>
       </c>
       <c r="X16" s="27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Y16" s="27"/>
-    </row>
-    <row r="17" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="Z16" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C17" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D17" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="30"/>
+      <c r="E17" s="40"/>
       <c r="F17" s="17" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>109</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>55</v>
@@ -1635,13 +1717,19 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="4:26" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C18" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D18" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="30"/>
+      <c r="E18" s="40"/>
       <c r="F18" s="17" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="G18" s="41" t="s">
+        <v>110</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>56</v>
@@ -1667,15 +1755,20 @@
       <c r="R18" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="W18" s="17" t="s">
-        <v>83</v>
+      <c r="W18" s="39" t="s">
+        <v>103</v>
       </c>
       <c r="X18" s="27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Y18" s="27"/>
-    </row>
-    <row r="19" spans="4:26" x14ac:dyDescent="0.3">
+      <c r="Z18" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="F19" s="42"/>
+      <c r="G19" s="41"/>
       <c r="L19" s="7" t="s">
         <v>1</v>
       </c>
@@ -1692,13 +1785,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="4:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C20" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D20" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="30"/>
+      <c r="E20" s="40"/>
       <c r="F20" s="17" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>111</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>52</v>
@@ -1728,20 +1827,26 @@
         <v>46</v>
       </c>
       <c r="W20" s="19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="X20" s="27" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="Y20" s="27"/>
     </row>
-    <row r="21" spans="4:26" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C21" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D21" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="30"/>
+      <c r="E21" s="40"/>
       <c r="F21" s="17" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="G21" s="41" t="s">
+        <v>112</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>51</v>
@@ -1771,21 +1876,27 @@
         <v>45</v>
       </c>
       <c r="W21" s="19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="X21" s="27"/>
       <c r="Y21" s="27"/>
       <c r="Z21" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="4:26" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C22" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D22" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="30"/>
+      <c r="E22" s="40"/>
       <c r="F22" s="17" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="G22" s="41" t="s">
+        <v>113</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>54</v>
@@ -1818,7 +1929,7 @@
         <v>51</v>
       </c>
       <c r="W22" s="19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="X22" s="27"/>
       <c r="Y22" s="27"/>
@@ -1826,13 +1937,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="4:26" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="C23" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D23" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="30"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="17" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="G23" s="41" t="s">
+        <v>114</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>53</v>
@@ -1865,14 +1982,16 @@
         <v>52</v>
       </c>
       <c r="W23" s="19" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="X23" s="27" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="Y23" s="27"/>
     </row>
-    <row r="24" spans="4:26" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="F24" s="42"/>
+      <c r="G24" s="41"/>
       <c r="L24" s="7" t="s">
         <v>1</v>
       </c>
@@ -1889,13 +2008,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D25" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="E25" s="30"/>
+      <c r="E25" s="40"/>
       <c r="F25" s="17" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="G25" s="41" t="s">
+        <v>115</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>52</v>
@@ -1928,20 +2053,26 @@
         <v>53</v>
       </c>
       <c r="W25" s="19" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="X25" s="27" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="Y25" s="27"/>
     </row>
-    <row r="26" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C26" s="7" t="s">
+        <v>97</v>
+      </c>
       <c r="D26" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="30"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="17" t="s">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="G26" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>51</v>
@@ -1976,14 +2107,17 @@
         <v>54</v>
       </c>
       <c r="W26" s="17" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="X26" s="27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Y26" s="27"/>
-    </row>
-    <row r="27" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Z26" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N27" s="11" t="s">
         <v>0</v>
       </c>
@@ -1994,9 +2128,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="4:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:26" x14ac:dyDescent="0.3">
       <c r="I32" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
